--- a/data/trans_dic/P55$amigo-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P55$amigo-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,91</t>
+          <t>0,0; 19,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,45</t>
+          <t>0,0; 46,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,31</t>
+          <t>0,0; 19,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,97; 16,65</t>
+          <t>2,91; 15,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,88</t>
+          <t>0,0; 25,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,49</t>
+          <t>0,0; 12,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 13,54</t>
+          <t>2,93; 12,95</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,64</t>
+          <t>0,0; 26,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,3</t>
+          <t>0,0; 21,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,11</t>
+          <t>0,0; 33,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,7</t>
+          <t>0,0; 11,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 9,85</t>
+          <t>1,08; 10,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,48</t>
+          <t>0,0; 10,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,18</t>
+          <t>0,0; 10,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 11,38</t>
+          <t>2,37; 12,49</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,97</t>
+          <t>0,0; 15,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,66</t>
+          <t>0,0; 22,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,51</t>
+          <t>0,0; 7,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,23</t>
+          <t>0,0; 10,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,71</t>
+          <t>0,0; 12,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,32</t>
+          <t>0,0; 4,95</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,65</t>
+          <t>0,0; 19,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,05</t>
+          <t>0,0; 6,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 4,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 4,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,49</t>
+          <t>0,0; 6,85</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,99</t>
+          <t>0,0; 37,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,09</t>
+          <t>0,0; 29,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,55</t>
+          <t>0,0; 11,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,06</t>
+          <t>0,0; 25,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 14,79</t>
+          <t>1,44; 13,75</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,79</t>
+          <t>0,0; 28,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,14; 17,75</t>
+          <t>2,17; 17,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,86</t>
+          <t>0,0; 24,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,3</t>
+          <t>0,0; 29,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,58</t>
+          <t>0,0; 6,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,64</t>
+          <t>0,0; 12,82</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,68</t>
+          <t>0,0; 13,29</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,05</t>
+          <t>0,0; 16,24</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,69; 10,11</t>
+          <t>1,82; 9,8</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,97</t>
+          <t>0,0; 14,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 4,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,84</t>
+          <t>0,0; 14,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,71; 20,84</t>
+          <t>6,93; 20,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 3,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0; 2,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 9,6</t>
+          <t>1,06; 10,83</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,59; 14,07</t>
+          <t>4,44; 14,41</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,32</t>
+          <t>0,0; 9,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,77</t>
+          <t>0,0; 44,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,48</t>
+          <t>0,0; 19,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,27</t>
+          <t>0,0; 10,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 4,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,27</t>
+          <t>0,0; 9,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,87; 12,51</t>
+          <t>1,76; 13,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,48</t>
+          <t>0,9; 8,74</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,53</t>
+          <t>0,0; 15,87</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,56</t>
+          <t>0,0; 8,52</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,06; 11,09</t>
+          <t>2,14; 11,38</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,81</t>
+          <t>0,0; 5,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,72; 10,12</t>
+          <t>0,71; 9,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,7</t>
+          <t>0,0; 5,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,25; 7,93</t>
+          <t>2,48; 8,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,04</t>
+          <t>0,89; 5,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,73</t>
+          <t>0,36; 2,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,88</t>
+          <t>0,93; 5,82</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,73; 7,48</t>
+          <t>3,63; 7,34</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,18</t>
+          <t>1,0; 3,87</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,36</t>
+          <t>0,74; 3,91</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,21</t>
+          <t>0,84; 4,06</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,6; 6,78</t>
+          <t>3,72; 6,81</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1624</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1709</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1412</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4843</t>
+          <t>0; 5389</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4757</t>
+          <t>0; 4787</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4639</t>
+          <t>0; 5425</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2241</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>978; 5477</t>
+          <t>956; 5248</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6973</t>
+          <t>0; 4839</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 5425</t>
+          <t>0; 4952</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 2012</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1797; 8113</t>
+          <t>1755; 7761</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4501</t>
+          <t>0; 4247</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6186</t>
+          <t>0; 4997</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1605</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5248</t>
+          <t>0; 5143</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1878</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4106</t>
+          <t>0; 5046</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2389</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>588; 5420</t>
+          <t>593; 5978</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4865</t>
+          <t>0; 4189</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 7361</t>
+          <t>0; 6835</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2181</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1746; 8012</t>
+          <t>1671; 8794</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1634</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1942</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1472</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1115</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5352</t>
+          <t>0; 5365</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5474</t>
+          <t>0; 6076</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2184</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3345</t>
+          <t>0; 3398</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4722</t>
+          <t>0; 4661</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 6016</t>
+          <t>0; 5277</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 1854</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3030</t>
+          <t>0; 3476</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1688</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1924</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1556</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3417</t>
+          <t>0; 3175</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1903</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 1983</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2237</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2174</t>
+          <t>0; 2501</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1883</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 2007</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 2019</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 3929</t>
+          <t>0; 3596</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1355</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1862</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1303</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3116</t>
+          <t>0; 3029</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 1848</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1923</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 7512</t>
+          <t>0; 7045</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 1702</t>
+          <t>0; 1901</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 1711</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 1979</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 6999</t>
+          <t>0; 7307</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>344; 3568</t>
+          <t>346; 3317</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1706</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5206</t>
+          <t>0; 5214</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1492</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>517; 4293</t>
+          <t>525; 4351</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 5832</t>
+          <t>0; 6866</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1926</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 6151</t>
+          <t>0; 6903</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 2393</t>
+          <t>0; 2205</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 5804</t>
+          <t>0; 5888</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 5779</t>
+          <t>0; 5230</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 5383</t>
+          <t>0; 6226</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>940; 5635</t>
+          <t>1017; 5463</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1693</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2069</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4486</t>
+          <t>0; 3766</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 1430</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 1969</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2144</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 8357</t>
+          <t>0; 7994</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3587; 11134</t>
+          <t>3705; 11118</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 1910</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 2153</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>867; 7947</t>
+          <t>875; 8964</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3523; 10787</t>
+          <t>3408; 11050</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 4005</t>
+          <t>0; 3212</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 8282</t>
+          <t>0; 9295</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 1745</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 3142</t>
+          <t>0; 3240</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 5361</t>
+          <t>0; 5137</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 2084</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 5158</t>
+          <t>0; 5553</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1099; 7352</t>
+          <t>1033; 7682</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>728; 6793</t>
+          <t>723; 6997</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 9836</t>
+          <t>0; 10750</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 6082</t>
+          <t>0; 6854</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1564; 8401</t>
+          <t>1619; 8618</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 6085</t>
+          <t>0; 6390</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1056; 14792</t>
+          <t>1039; 14098</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0; 4488</t>
+          <t>0; 6211</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3529; 12456</t>
+          <t>3890; 12919</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2104; 11637</t>
+          <t>2066; 11894</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>992; 7624</t>
+          <t>994; 8357</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3454; 15713</t>
+          <t>2478; 15565</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>12238; 24564</t>
+          <t>11911; 24099</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3620; 14944</t>
+          <t>3573; 13827</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3229; 18581</t>
+          <t>3156; 16662</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3582; 16351</t>
+          <t>3260; 15803</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>17464; 32884</t>
+          <t>18037; 33050</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$amigo-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P55$amigo-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -732,17 +732,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,93</t>
+          <t>0,0; 17,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,74</t>
+          <t>0,0; 47,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,08</t>
+          <t>0,0; 21,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,17 +752,17 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,91; 15,95</t>
+          <t>2,86; 15,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,59</t>
+          <t>0,0; 25,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,31</t>
+          <t>0,0; 13,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,93; 12,95</t>
+          <t>2,68; 12,15</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,09</t>
+          <t>0,0; 32,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,25</t>
+          <t>0,0; 29,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,43</t>
+          <t>0,0; 33,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,92</t>
+          <t>0,0; 9,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,17 +892,17 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 10,87</t>
+          <t>1,04; 10,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,75</t>
+          <t>0,0; 12,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,38</t>
+          <t>0,0; 9,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 12,49</t>
+          <t>2,04; 11,5</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,01</t>
+          <t>0,0; 15,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,94</t>
+          <t>0,0; 20,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,63</t>
+          <t>0,0; 7,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,1</t>
+          <t>0,0; 9,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,9</t>
+          <t>0,0; 13,78</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,95</t>
+          <t>0,0; 4,62</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,19</t>
+          <t>0,0; 17,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,96</t>
+          <t>0,0; 6,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,85</t>
+          <t>0,0; 6,2</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,9</t>
+          <t>0,0; 37,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1307,12 +1307,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,16</t>
+          <t>0,0; 29,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,78</t>
+          <t>0,0; 9,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1327,12 +1327,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,12</t>
+          <t>0,0; 25,15</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 13,75</t>
+          <t>1,33; 13,79</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,83</t>
+          <t>0,0; 28,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,17; 17,99</t>
+          <t>2,12; 17,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,56</t>
+          <t>0,0; 21,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1447,32 +1447,32 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,51</t>
+          <t>0,0; 29,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,99</t>
+          <t>0,0; 8,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,82</t>
+          <t>0,0; 14,78</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,29</t>
+          <t>0,0; 14,59</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,24</t>
+          <t>0,0; 13,85</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,82; 9,8</t>
+          <t>1,66; 9,21</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,25</t>
+          <t>0,0; 14,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,19</t>
+          <t>0,0; 12,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,93; 20,81</t>
+          <t>6,18; 19,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1607,12 +1607,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 10,83</t>
+          <t>1,08; 10,98</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,44; 14,41</t>
+          <t>4,21; 12,99</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,88</t>
+          <t>0,0; 11,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,63</t>
+          <t>0,0; 44,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,06</t>
+          <t>0,0; 17,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,8</t>
+          <t>0,0; 11,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1727,32 +1727,32 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,98</t>
+          <t>0,0; 9,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,76; 13,07</t>
+          <t>1,86; 15,67</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,9; 8,74</t>
+          <t>0,9; 9,19</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,87</t>
+          <t>0,0; 16,48</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,52</t>
+          <t>0,0; 7,94</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,14; 11,38</t>
+          <t>2,13; 12,99</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,05</t>
+          <t>0,0; 4,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,71; 9,64</t>
+          <t>0,71; 9,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,11</t>
+          <t>0,0; 3,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,48; 8,22</t>
+          <t>2,39; 7,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,15</t>
+          <t>0,91; 5,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,99</t>
+          <t>0,35; 3,06</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,82</t>
+          <t>0,92; 5,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,63; 7,34</t>
+          <t>3,7; 7,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,87</t>
+          <t>0,91; 3,99</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,91</t>
+          <t>0,72; 3,95</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,06</t>
+          <t>0,92; 4,27</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,81</t>
+          <t>3,53; 6,74</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>2447</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>3884</t>
         </is>
       </c>
     </row>
@@ -2224,17 +2224,17 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5389</t>
+          <t>0; 5050</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4787</t>
+          <t>0; 4849</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5425</t>
+          <t>0; 6068</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -2244,17 +2244,17 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>956; 5248</t>
+          <t>961; 5254</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4839</t>
+          <t>0; 4739</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 4952</t>
+          <t>0; 5538</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1755; 7761</t>
+          <t>1686; 7634</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4241</t>
         </is>
       </c>
     </row>
@@ -2417,12 +2417,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4247</t>
+          <t>0; 5215</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4997</t>
+          <t>0; 7044</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5143</t>
+          <t>0; 5578</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5046</t>
+          <t>0; 4146</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2452,17 +2452,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>593; 5978</t>
+          <t>609; 5896</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4189</t>
+          <t>0; 4699</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 6835</t>
+          <t>0; 6505</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1671; 8794</t>
+          <t>1531; 8622</t>
         </is>
       </c>
     </row>
@@ -2645,12 +2645,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5365</t>
+          <t>0; 5390</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6076</t>
+          <t>0; 5530</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2660,17 +2660,17 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3398</t>
+          <t>0; 3530</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4661</t>
+          <t>0; 4600</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 5277</t>
+          <t>0; 5634</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3476</t>
+          <t>0; 3229</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>616</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>487</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1102</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3175</t>
+          <t>0; 3166</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2501</t>
+          <t>0; 2594</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 3596</t>
+          <t>0; 3454</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>999</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>330</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1329</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3029</t>
+          <t>0; 3062</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 7045</t>
+          <t>0; 7188</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 1901</t>
+          <t>0; 1648</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 7307</t>
+          <t>0; 7316</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>346; 3317</t>
+          <t>331; 3448</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>755</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2677</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5214</t>
+          <t>0; 5234</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>525; 4351</t>
+          <t>513; 4338</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6866</t>
+          <t>0; 5959</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -3279,32 +3279,32 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 6903</t>
+          <t>0; 6816</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 2205</t>
+          <t>0; 2832</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 5888</t>
+          <t>0; 6787</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 5230</t>
+          <t>0; 5743</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 6226</t>
+          <t>0; 5309</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1017; 5463</t>
+          <t>938; 5191</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>7397</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3766</t>
+          <t>0; 3740</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3487,12 +3487,12 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 7994</t>
+          <t>0; 6840</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3705; 11118</t>
+          <t>4033; 12490</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>875; 8964</t>
+          <t>894; 9083</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3408; 11050</t>
+          <t>3954; 12190</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>736</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>4862</t>
         </is>
       </c>
     </row>
@@ -3665,12 +3665,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3212</t>
+          <t>0; 3641</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 9295</t>
+          <t>0; 9356</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 3240</t>
+          <t>0; 3397</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 5137</t>
+          <t>0; 5631</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3695,32 +3695,32 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 5553</t>
+          <t>0; 5486</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1033; 7682</t>
+          <t>1270; 10704</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>723; 6997</t>
+          <t>724; 7359</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 10750</t>
+          <t>0; 11157</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 6854</t>
+          <t>0; 6382</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1619; 8618</t>
+          <t>1870; 11395</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>17165</t>
+          <t>18879</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>24716</t>
+          <t>26440</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 6390</t>
+          <t>0; 5643</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1039; 14098</t>
+          <t>1040; 13502</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0; 6211</t>
+          <t>0; 4106</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3890; 12919</t>
+          <t>4040; 12583</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2066; 11894</t>
+          <t>2095; 11614</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>994; 8357</t>
+          <t>985; 8554</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2478; 15565</t>
+          <t>2472; 14437</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>11911; 24099</t>
+          <t>13233; 26954</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3573; 13827</t>
+          <t>3256; 14253</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3156; 16662</t>
+          <t>3047; 16801</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3260; 15803</t>
+          <t>3582; 16601</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>18037; 33050</t>
+          <t>18597; 35462</t>
         </is>
       </c>
     </row>
